--- a/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>ANNX</t>
   </si>
@@ -656,114 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -833,8 +840,14 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -904,8 +917,14 @@
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -975,8 +994,14 @@
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,79 +1027,87 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F12" s="3">
         <v>27900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>30300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>32300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>28500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>27900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>29100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>27000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>27200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>27600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>24600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>20700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>18000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>11800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>9300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>10200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>6800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>7100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>6000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>4700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>3900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>3800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1177,14 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1176,11 +1215,11 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
@@ -1194,29 +1233,35 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
         <v>-200</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1286,8 +1331,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,79 +1361,87 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>30000</v>
+      </c>
+      <c r="F17" s="3">
         <v>34800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>37700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>41200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>36700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>36100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>37400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>35400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>37500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>35700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>31400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>26200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>23200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>15600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>12200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>12500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>8900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>9100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>8200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>6100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>4900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1390,70 +1449,76 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="G18" s="3">
         <v>-37700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-41200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-36700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-36100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-37400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-35400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-37500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-35700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-31400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-26200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-23200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-12200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-12500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-8900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-9100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-8200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-6100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-4900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1544,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1488,25 +1555,25 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
@@ -1518,40 +1585,46 @@
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-2500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1559,70 +1632,76 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="G21" s="3">
         <v>-34700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-38100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-33900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-34500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-36600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-34900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-36900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-35000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-30800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-25500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-22900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-15500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-12100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-12200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-8800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-10100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-9300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-8500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-4500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1692,111 +1771,123 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-32500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-35200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-38700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-34400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-35100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-37100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-35400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-37400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-35600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-31300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-26100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-23200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-12200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-12300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-8900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-10200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-9400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-8700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-4700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1834,8 +1925,14 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +2002,168 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-32500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-35200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-38700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-34400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-35100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-37100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-35400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-37400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-35600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-31300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-26100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-23200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-12200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-12300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-8900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-10200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-9400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-8700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-4700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-32500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-35200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-38700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-34400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-35100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-37100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-35400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-37400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-35600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-31300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-26100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-23200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-12500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-12600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-9200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-10500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-9700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-8900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-4800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2233,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2310,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2387,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2464,14 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2340,25 +2479,25 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
@@ -2370,111 +2509,123 @@
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>2500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-32500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-35200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-38700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-34400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-35100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-37100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-35400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-37400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-35600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-31300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-26100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-23200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-12500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-12600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-9200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-10500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-9700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-8900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-4800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2695,173 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-32500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-35200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-38700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-34400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-35100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-37100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-35400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-37400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-35600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-31300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-26100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-23200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-12500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-12600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-9200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-10500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-9700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-8900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-4800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2887,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,124 +2916,132 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>151900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>225100</v>
+      </c>
+      <c r="F41" s="3">
         <v>133200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>113600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>144100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>140000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>210700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>104600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>112800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>74800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>68500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>99600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>206700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>268600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>370700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>124800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>33300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>43900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>53700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>31500</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>34600</v>
+      </c>
+      <c r="F42" s="3">
         <v>32100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>79300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>84000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>102600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>58900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>73000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>93800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>167900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>202800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>202800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>120000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>82600</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2872,11 +3051,11 @@
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2887,8 +3066,14 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2917,14 +3102,14 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
@@ -2938,28 +3123,34 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3029,150 +3220,168 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F45" s="3">
         <v>3900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>5400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>5000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>3900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1800</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>270700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>263900</v>
+      </c>
+      <c r="F46" s="3">
         <v>169200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>197600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>232500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>248100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>274800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>181400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>211300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>247700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>275500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>304400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>330500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>354000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>373600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>125700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>34500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>45400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>54700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>33500</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3242,70 +3451,76 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>32800</v>
+      </c>
+      <c r="F48" s="3">
         <v>33600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>34400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>35200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>36000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>36700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>37300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>37900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>38200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>32900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>26200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1900</v>
-      </c>
-      <c r="P48" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>2000</v>
       </c>
       <c r="R48" s="3">
         <v>2000</v>
       </c>
       <c r="S48" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="T48" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="U48" s="3">
         <v>2100</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>4</v>
+      <c r="V48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="W48" s="3">
+        <v>2100</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>4</v>
@@ -3313,8 +3528,14 @@
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3384,8 +3605,14 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3682,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,13 +3759,19 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="E52" s="3">
         <v>1000</v>
@@ -3544,61 +3783,67 @@
         <v>1000</v>
       </c>
       <c r="H52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1800</v>
       </c>
       <c r="M52" s="3">
         <v>1200</v>
       </c>
       <c r="N52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O52" s="3">
         <v>1200</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>3400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3913,91 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>304100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>297700</v>
+      </c>
+      <c r="F54" s="3">
         <v>203800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>233000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>268800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>285100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>312700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>220700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>250600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>287000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>310200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>331800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>333100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>355900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>375600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>131100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>39500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>49900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>58600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>35700</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +4023,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,79 +4052,87 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F57" s="3">
         <v>4800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>10300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>7400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>10300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>4000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>3300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2200</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3935,150 +4202,168 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E59" s="3">
         <v>12400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
+        <v>12400</v>
+      </c>
+      <c r="G59" s="3">
         <v>10700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>12600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>14900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>13300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>10000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>7700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>10600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>7100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>6100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>6200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>6900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>9600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>3100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1700</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>17200</v>
+        <v>13100</v>
       </c>
       <c r="E60" s="3">
         <v>17900</v>
       </c>
       <c r="F60" s="3">
+        <v>17200</v>
+      </c>
+      <c r="G60" s="3">
+        <v>17900</v>
+      </c>
+      <c r="H60" s="3">
         <v>22900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>22400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>20200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>20300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>17100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>21700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>11900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>10300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>10700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>10600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>9000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>12700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>6300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3900</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4148,79 +4433,91 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>29200</v>
+      </c>
+      <c r="F62" s="3">
         <v>29800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>30400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>31000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>31500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>31900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>32400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>32900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>33400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>33800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>26200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1600</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4587,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4664,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4741,91 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>47100</v>
+      </c>
+      <c r="F66" s="3">
         <v>47000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>48300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>53900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>53900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>52100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>52700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>50000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>55100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>45700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>36400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>11600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>11700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>13900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>7700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>6400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>6700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>5500</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4851,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4924,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +5001,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4717,34 +5052,40 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>235100</v>
       </c>
-      <c r="R70" s="3">
+      <c r="T70" s="3">
         <v>144300</v>
       </c>
-      <c r="S70" s="3">
+      <c r="U70" s="3">
         <v>144000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="V70" s="3">
         <v>143700</v>
       </c>
-      <c r="U70" s="3">
+      <c r="W70" s="3">
         <v>112100</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +5155,91 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-597700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-572500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-544600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-512100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-476900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-438300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-403900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-368800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-331700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-296300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-258900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-223300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-192000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-166000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-142800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-127200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-114900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-102600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-93600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-83500</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5309,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5386,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5463,91 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>262400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>250600</v>
+      </c>
+      <c r="F76" s="3">
         <v>156800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>184700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>214900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>231200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>260600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>168000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>200600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>231900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>264500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>295300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>321500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>344300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>365500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-117900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-112400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-100500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-91800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-81900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5617,173 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-32500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-35200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-38700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-34400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-35100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-37100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-35400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-37400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-35600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-31300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-26100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-23200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-12500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-12600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-9200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-10500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-9700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-8900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-4800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5809,10 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5444,22 +5841,22 @@
         <v>500</v>
       </c>
       <c r="L83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M83" s="3">
         <v>500</v>
       </c>
       <c r="N83" s="3">
+        <v>600</v>
+      </c>
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q83" s="3">
         <v>300</v>
-      </c>
-      <c r="P83" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
@@ -5483,10 +5880,16 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5959,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +6036,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +6113,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +6190,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,8 +6267,14 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5849,70 +6282,76 @@
         <v>-28300</v>
       </c>
       <c r="E89" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="G89" s="3">
         <v>-36400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-33000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-27100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-30700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-28200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-30300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-28300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-29700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-24700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-23400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-19300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-10200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-10000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-8800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-6900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-6700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-6000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-4900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6377,10 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5950,67 +6391,73 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-5200</v>
       </c>
       <c r="K91" s="3">
         <v>-900</v>
       </c>
       <c r="L91" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6527,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6604,91 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-77300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F94" s="3">
         <v>47800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>5500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>19500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-43600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>14100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>19700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>68300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>33700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-83100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-37600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-82900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6714,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6787,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6864,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6941,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,79 +7018,91 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>32400</v>
       </c>
       <c r="E100" s="3">
+        <v>117600</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>17600</v>
-      </c>
-      <c r="G100" s="3">
-        <v>100</v>
-      </c>
-      <c r="H100" s="3">
-        <v>122700</v>
       </c>
       <c r="I100" s="3">
         <v>100</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>122700</v>
       </c>
       <c r="K100" s="3">
+        <v>100</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>259800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>101700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>29200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>44800</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6675,75 +7172,87 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-73200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>92000</v>
+      </c>
+      <c r="F102" s="3">
         <v>19500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-30500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>4100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-70600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>106000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-8300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>38000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>6300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-31100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-107100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-60700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-102100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>245900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>91400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-10600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-9700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>22200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-6700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-6000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>39900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>ANNX</t>
   </si>
@@ -656,121 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -846,8 +850,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -923,8 +930,11 @@
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1000,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E12" s="3">
         <v>21000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>32300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>28500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>27900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>27000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>20700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>18000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1221,8 +1241,8 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
@@ -1239,29 +1259,32 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,85 +1389,89 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E17" s="3">
         <v>28600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>30000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>37700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>36700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>36100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>35400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>35700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>31400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1449,76 +1479,79 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-30000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-34800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-37700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-41200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-36700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-36100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-37400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-35400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-37500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-35700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-31400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-26200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-23200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-12200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-12500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1555,28 +1589,28 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F20" s="3">
         <v>2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
@@ -1591,40 +1625,43 @@
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1632,76 +1669,79 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-27400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-31900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-34700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-38100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-33900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-34500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-36600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-34900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-36900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-35000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-30800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-22900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-15500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-12100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-12200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-10100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1777,85 +1817,91 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-32500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-38700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-34400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-35100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-37100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-35400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-37400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-35600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-31300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-23200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-12200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-9400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1880,8 +1926,8 @@
       <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>4</v>
@@ -1889,8 +1935,8 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1931,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-27900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-32500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-35200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-38700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-35100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-37100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-35400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-37400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-35600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-31300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-15600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-12200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-12300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-27900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-32500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-35200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-38700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-35100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-37100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-35400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-37400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-35600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-23200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-22000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-12500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-12600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2479,28 +2549,28 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
@@ -2515,117 +2585,123 @@
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-32500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-35200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-38700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-35100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-37100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-35400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-37400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-35600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-23200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-22000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-12500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-12600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-32500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-35200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-38700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-35100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-37100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-35400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-37400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-35600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-23200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-22000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-12500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-12600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,74 +3004,75 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>157300</v>
+      </c>
+      <c r="E41" s="3">
         <v>151900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>225100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>133200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>113600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>144100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>140000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>210700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>104600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>112800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>74800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>68500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>99600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>206700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>268600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>370700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>124800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>33300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>43900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>53700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>31500</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2995,56 +3082,59 @@
       <c r="AA41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>211400</v>
+      </c>
+      <c r="E42" s="3">
         <v>113000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>34600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>32100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>79300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>84000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>102600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>58900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>73000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>93800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>167900</v>
-      </c>
-      <c r="N42" s="3">
-        <v>202800</v>
       </c>
       <c r="O42" s="3">
         <v>202800</v>
       </c>
       <c r="P42" s="3">
+        <v>202800</v>
+      </c>
+      <c r="Q42" s="3">
         <v>120000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>82600</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3057,8 +3147,8 @@
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3072,8 +3162,11 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3108,11 +3201,11 @@
         <v>0</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -3129,16 +3222,16 @@
         <v>0</v>
       </c>
       <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>100</v>
-      </c>
-      <c r="V43" s="3">
-        <v>200</v>
       </c>
       <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>4</v>
+      <c r="X43" s="3">
+        <v>200</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>4</v>
@@ -3149,8 +3242,11 @@
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3226,74 +3322,77 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E45" s="3">
         <v>5800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1800</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3303,74 +3402,77 @@
       <c r="AA45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E46" s="3">
         <v>270700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>263900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>169200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>197600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>232500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>248100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>274800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>181400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>211300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>247700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>275500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>304400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>330500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>354000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>373600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>125700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>34500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>45400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>54700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>33500</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3380,8 +3482,11 @@
       <c r="AA46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3457,55 +3562,58 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E48" s="3">
         <v>31900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1900</v>
-      </c>
-      <c r="R48" s="3">
-        <v>2000</v>
       </c>
       <c r="S48" s="3">
         <v>2000</v>
@@ -3514,17 +3622,17 @@
         <v>2000</v>
       </c>
       <c r="U48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="V48" s="3">
         <v>2100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2100</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3534,8 +3642,11 @@
       <c r="AA48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,16 +3882,19 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1400</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1000</v>
       </c>
       <c r="F52" s="3">
         <v>1000</v>
@@ -3789,50 +3909,50 @@
         <v>1000</v>
       </c>
       <c r="J52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K52" s="3">
         <v>1200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1800</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1200</v>
       </c>
       <c r="P52" s="3">
         <v>1200</v>
       </c>
       <c r="Q52" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>3400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>100</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,74 +4042,77 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>406100</v>
+      </c>
+      <c r="E54" s="3">
         <v>304100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>297700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>203800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>233000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>268800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>285100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>312700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>220700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>250600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>287000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>310200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>331800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>333100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>355900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>375600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>131100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>39500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>49900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>58600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35700</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,74 +4184,75 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E57" s="3">
         <v>4000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2200</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4131,8 +4262,11 @@
       <c r="AA57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4208,74 +4342,77 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E59" s="3">
         <v>9200</v>
-      </c>
-      <c r="E59" s="3">
-        <v>12400</v>
       </c>
       <c r="F59" s="3">
         <v>12400</v>
       </c>
       <c r="G59" s="3">
+        <v>12400</v>
+      </c>
+      <c r="H59" s="3">
         <v>10700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3100</v>
-      </c>
-      <c r="U59" s="3">
-        <v>2600</v>
       </c>
       <c r="V59" s="3">
         <v>2600</v>
       </c>
       <c r="W59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="X59" s="3">
         <v>1700</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4285,74 +4422,77 @@
       <c r="AA59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E60" s="3">
         <v>13100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3900</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4362,8 +4502,11 @@
       <c r="AA60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4439,74 +4582,77 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E62" s="3">
         <v>28500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>29200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>29800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>30400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>31000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>31500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>31900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>32400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>32900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>33400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>33800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1600</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,74 +4902,77 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E66" s="3">
         <v>41700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48300</v>
-      </c>
-      <c r="H66" s="3">
-        <v>53900</v>
       </c>
       <c r="I66" s="3">
         <v>53900</v>
       </c>
       <c r="J66" s="3">
+        <v>53900</v>
+      </c>
+      <c r="K66" s="3">
         <v>52100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>50000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>36400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5500</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5058,23 +5226,23 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>235100</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>144300</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>144000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>143700</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>112100</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,74 +5332,77 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-627300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-597700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-572500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-544600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-512100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-476900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-438300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-403900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-368800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-331700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-296300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-258900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-223300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-192000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-166000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-142800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-127200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-114900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-102600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-93600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-83500</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,74 +5652,77 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>361100</v>
+      </c>
+      <c r="E76" s="3">
         <v>262400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>250600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>156800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>184700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>214900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>231200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>260600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>168000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>200600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>231900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>264500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>295300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>321500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>344300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>365500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-117900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-112400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-100500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-91800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-81900</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-32500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-35200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-38700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-35100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-37100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-35400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-37400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-35600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-23200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-22000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-12500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-12600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5847,19 +6046,19 @@
         <v>500</v>
       </c>
       <c r="N83" s="3">
+        <v>500</v>
+      </c>
+      <c r="O83" s="3">
         <v>600</v>
-      </c>
-      <c r="O83" s="3">
-        <v>500</v>
       </c>
       <c r="P83" s="3">
         <v>500</v>
       </c>
       <c r="Q83" s="3">
+        <v>500</v>
+      </c>
+      <c r="R83" s="3">
         <v>300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
@@ -5886,10 +6085,13 @@
         <v>100</v>
       </c>
       <c r="AA83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-28300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-23500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-36400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-33000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-27100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-28300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-29700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-24700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-19300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-13600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-10200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6599,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6397,58 +6618,58 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,76 +6837,79 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-96600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-77300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>47800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>5500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>19500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-43600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>14100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>19700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>68300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>33700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-83100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-82900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,85 +7267,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>123700</v>
+      </c>
+      <c r="E100" s="3">
         <v>32400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>117600</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>17600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>122700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>259800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>101700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>29200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>44800</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7178,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-73200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>92000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-70600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>106000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>38000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-107100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-60700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-102100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>245900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>91400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>22200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>39900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
   <si>
     <t>ANNX</t>
   </si>
@@ -656,148 +656,152 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -853,8 +857,11 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -933,8 +940,11 @@
       <c r="AB9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1013,8 +1023,11 @@
       <c r="AB10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E12" s="3">
         <v>25000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>27900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>30300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>28500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>27900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>18000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>11800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,31 +1220,34 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1244,8 +1264,8 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
@@ -1262,52 +1282,55 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W14" s="3">
         <v>-200</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E17" s="3">
         <v>33600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>30000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>37700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>36700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>35400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>37500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>35700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-39400</v>
       </c>
       <c r="E18" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-28600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-30000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-34800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-37700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-41200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-36700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-36100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-37400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-35400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-37500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-35700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-26200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-23200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-12200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-12500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,40 +1613,41 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>2300</v>
       </c>
-      <c r="H20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
@@ -1628,143 +1662,149 @@
         <v>100</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-38900</v>
       </c>
       <c r="E21" s="3">
-        <v>-24600</v>
+        <v>-33000</v>
       </c>
       <c r="F21" s="3">
-        <v>-27400</v>
+        <v>-28000</v>
       </c>
       <c r="G21" s="3">
-        <v>-31900</v>
+        <v>-29500</v>
       </c>
       <c r="H21" s="3">
-        <v>-34700</v>
+        <v>-34200</v>
       </c>
       <c r="I21" s="3">
-        <v>-38100</v>
+        <v>-37200</v>
       </c>
       <c r="J21" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="K21" s="3">
         <v>-33900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-34500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-36600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-34900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-36900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-35000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-30800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-25500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-22900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-15500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-12100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-12200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-8800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-10100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1820,117 +1860,123 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-29600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-27900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-35200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-38700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-34400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-35100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-37100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-35400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-37400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-35600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-26100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-23200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-12300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>4</v>
@@ -1938,8 +1984,8 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1980,8 +2026,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-29600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-27900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-35200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-35100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-37100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-35400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-37400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-35600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-23200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-15600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-12200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-12300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-29600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-27900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-32500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-35200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-34400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-35100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-37100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-35400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-37400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-35600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-23200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-22000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-12500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,40 +2607,43 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2300</v>
       </c>
-      <c r="H32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
@@ -2588,120 +2658,126 @@
         <v>-100</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-29600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-27900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-32500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-35200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-34400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-35100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-37100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-35400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-37400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-35600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-23200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-22000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-12500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-29600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-27900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-32500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-35200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-34400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-35100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-37100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-35400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-37400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-35600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-23200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-22000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-12500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,77 +3091,78 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>79500</v>
+      </c>
+      <c r="E41" s="3">
         <v>157300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>151900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>225100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>133200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>113600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>144100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>140000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>210700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>104600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>74800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>68500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>99600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>206700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>268600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>370700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>124800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>33300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>43900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>53700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>31500</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3085,59 +3172,62 @@
       <c r="AB41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>260600</v>
+      </c>
+      <c r="E42" s="3">
         <v>211400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>113000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>34600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>32100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>79300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>84000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>102600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>58900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>73000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>93800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>167900</v>
-      </c>
-      <c r="O42" s="3">
-        <v>202800</v>
       </c>
       <c r="P42" s="3">
         <v>202800</v>
       </c>
       <c r="Q42" s="3">
+        <v>202800</v>
+      </c>
+      <c r="R42" s="3">
         <v>120000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>82600</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3150,8 +3240,8 @@
       <c r="W42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3165,31 +3255,34 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3204,11 +3297,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -3225,16 +3318,16 @@
         <v>0</v>
       </c>
       <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>100</v>
-      </c>
-      <c r="W43" s="3">
-        <v>200</v>
       </c>
       <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>4</v>
+      <c r="Y43" s="3">
+        <v>200</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>4</v>
@@ -3245,31 +3338,34 @@
       <c r="AB43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3325,77 +3421,80 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>200</v>
+      </c>
+      <c r="K45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L45" s="3">
         <v>5300</v>
       </c>
-      <c r="E45" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="M45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N45" s="3">
+        <v>4600</v>
+      </c>
+      <c r="O45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="P45" s="3">
         <v>3900</v>
       </c>
-      <c r="H45" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>5400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>5300</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="Q45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R45" s="3">
         <v>3800</v>
       </c>
-      <c r="M45" s="3">
-        <v>4600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>5000</v>
-      </c>
-      <c r="O45" s="3">
-        <v>3900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>3800</v>
-      </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1800</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3405,77 +3504,80 @@
       <c r="AB45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>344300</v>
+      </c>
+      <c r="E46" s="3">
         <v>374000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>270700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>263900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>169200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>197600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>232500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>248100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>274800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>181400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>211300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>247700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>275500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>304400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>330500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>354000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>373600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>125700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>34500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>45400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>54700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>33500</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3485,31 +3587,34 @@
       <c r="AB46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3565,58 +3670,61 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E48" s="3">
         <v>31100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>33600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1900</v>
-      </c>
-      <c r="S48" s="3">
-        <v>2000</v>
       </c>
       <c r="T48" s="3">
         <v>2000</v>
@@ -3625,17 +3733,17 @@
         <v>2000</v>
       </c>
       <c r="V48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W48" s="3">
         <v>2100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2100</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3645,8 +3753,11 @@
       <c r="AB48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,19 +4002,22 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1000</v>
       </c>
       <c r="G52" s="3">
         <v>1000</v>
@@ -3912,50 +4032,50 @@
         <v>1000</v>
       </c>
       <c r="K52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L52" s="3">
         <v>1200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1800</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1200</v>
       </c>
       <c r="Q52" s="3">
         <v>1200</v>
       </c>
       <c r="R52" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>3400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,77 +4168,80 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>378800</v>
+      </c>
+      <c r="E54" s="3">
         <v>406100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>304100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>297700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>203800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>233000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>268800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>285100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>312700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>220700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>250600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>287000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>310200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>331800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>333100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>355900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>375600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>131100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>39500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>49900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35700</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,77 +4315,78 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E57" s="3">
         <v>4100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2200</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4265,31 +4396,34 @@
       <c r="AB57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4345,77 +4479,80 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>13000</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E59" s="3">
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>12400</v>
+        <v>100</v>
       </c>
       <c r="G59" s="3">
-        <v>12400</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>10700</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
-        <v>12600</v>
+        <v>200</v>
       </c>
       <c r="J59" s="3">
+        <v>400</v>
+      </c>
+      <c r="K59" s="3">
         <v>14900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3100</v>
-      </c>
-      <c r="V59" s="3">
-        <v>2600</v>
       </c>
       <c r="W59" s="3">
         <v>2600</v>
       </c>
       <c r="X59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Y59" s="3">
         <v>1700</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4425,77 +4562,80 @@
       <c r="AB59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E60" s="3">
         <v>17100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3900</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4505,31 +4645,34 @@
       <c r="AB60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>27200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>27900</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>29200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>29800</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>30400</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4585,77 +4728,80 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>27900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>28500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>29200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>29800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>30400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>31000</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>31500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>31900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>32400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>32900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>33400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>33800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>26200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1600</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,77 +5060,80 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E66" s="3">
         <v>45000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48300</v>
-      </c>
-      <c r="I66" s="3">
-        <v>53900</v>
       </c>
       <c r="J66" s="3">
         <v>53900</v>
       </c>
       <c r="K66" s="3">
+        <v>53900</v>
+      </c>
+      <c r="L66" s="3">
         <v>52100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>50000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>36400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5229,23 +5397,23 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>235100</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>144300</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>144000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>143700</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>112100</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,77 +5506,80 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-662100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-627300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-597700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-572500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-544600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-512100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-476900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-438300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-403900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-368800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-331700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-296300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-258900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-223300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-192000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-166000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-142800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-127200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-114900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-102600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-93600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-83500</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,77 +5838,80 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>331600</v>
+      </c>
+      <c r="E76" s="3">
         <v>361100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>262400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>250600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>156800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>184700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>214900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>231200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>260600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>168000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>200600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>231900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>264500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>295300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>321500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>344300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>365500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-117900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-112400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-100500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-91800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-81900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-29600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-27900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-32500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-35200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-34400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-35100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-37100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-35400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-37400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-35600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-23200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-22000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-12500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6208,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6049,19 +6248,19 @@
         <v>500</v>
       </c>
       <c r="O83" s="3">
+        <v>500</v>
+      </c>
+      <c r="P83" s="3">
         <v>600</v>
-      </c>
-      <c r="P83" s="3">
-        <v>500</v>
       </c>
       <c r="Q83" s="3">
         <v>500</v>
       </c>
       <c r="R83" s="3">
+        <v>500</v>
+      </c>
+      <c r="S83" s="3">
         <v>300</v>
-      </c>
-      <c r="S83" s="3">
-        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
@@ -6088,10 +6287,13 @@
         <v>100</v>
       </c>
       <c r="AB83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-21700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-28300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-28300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-36400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-33000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-27100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-28200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-30300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-29700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-23400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-19300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-13600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-10000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,19 +6820,20 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -6621,58 +6842,58 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,79 +7067,82 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-45900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-96600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-77300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>47800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>5500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>19500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-43600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>14100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>19700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>68300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>33700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-83100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-37600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-82900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,31 +7183,32 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,88 +7513,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>123700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>32400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>117600</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>17600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>122700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>259800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>101700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>29200</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>44800</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7430,84 +7679,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-77800</v>
+      </c>
+      <c r="E102" s="3">
         <v>5400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-73200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>92000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-30500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-70600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>106000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>38000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-31100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-107100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-60700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-102100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>245900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>91400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-10600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>22200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>39900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>ANNX</t>
   </si>
@@ -656,129 +656,132 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -803,8 +806,8 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -860,8 +863,11 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -943,8 +949,11 @@
       <c r="AC9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1026,8 +1035,11 @@
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,91 +1069,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E12" s="3">
         <v>30100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>21000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>27900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>28500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>27900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>18000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>11800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1239,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1249,8 +1268,8 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1267,8 +1286,8 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
@@ -1285,29 +1304,32 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3">
         <v>-200</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>4</v>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1333,7 +1355,7 @@
         <v>500</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1389,8 +1411,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E17" s="3">
         <v>39400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>30000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>34800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>37700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>35400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>31400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-39400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-33600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-28600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-30000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-34800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-37700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-41200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-36700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-36100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-37400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-35400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-37500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-31400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-26200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-23200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-15600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-12200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-12500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1646,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1640,17 +1673,17 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>2300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
@@ -1665,123 +1698,129 @@
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-51900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-38900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-33000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-28000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-29500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-34200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-37200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-40700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-33900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-34500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-36600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-34900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-36900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-35000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-30800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-25500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-22900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-15500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-12100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-12200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-8800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1806,8 +1845,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1863,91 +1902,97 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-34800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-29600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-27900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-35200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-38700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-34400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-35100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-37100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-35400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-37400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-35600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-31300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-26100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-12200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-12300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1972,14 +2017,14 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>4</v>
@@ -1987,8 +2032,8 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2029,8 +2074,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-34800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-29600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-27900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-32500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-35200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-38700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-34400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-35100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-37100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-35400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-37400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-35600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-31300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-26100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-15600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-12200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-29600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-32500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-35200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-38700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-34400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-35100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-37100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-35400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-37400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-35600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-31300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-26100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-23200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-22000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2676,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2636,17 +2705,17 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
@@ -2661,123 +2730,129 @@
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-29600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-32500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-35200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-38700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-34400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-35100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-37100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-35400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-37400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-35600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-31300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-26100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-22000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-29600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-32500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-35200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-38700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-34400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-35100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-37100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-35400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-37400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-35600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-31300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-26100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-22000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,80 +3177,81 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E41" s="3">
         <v>79500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>157300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>151900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>225100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>133200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>113600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>144100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>140000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>210700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>104600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>112800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>74800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>68500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>99600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>206700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>268600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>370700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>124800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>33300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>43900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>53700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>31500</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3175,62 +3261,65 @@
       <c r="AC41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>262500</v>
+      </c>
+      <c r="E42" s="3">
         <v>260600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>211400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>113000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>34600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>32100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>79300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>84000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>102600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>58900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>73000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>93800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>167900</v>
-      </c>
-      <c r="P42" s="3">
-        <v>202800</v>
       </c>
       <c r="Q42" s="3">
         <v>202800</v>
       </c>
       <c r="R42" s="3">
+        <v>202800</v>
+      </c>
+      <c r="S42" s="3">
         <v>120000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>82600</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3243,8 +3332,8 @@
       <c r="X42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3258,8 +3347,11 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3284,8 +3376,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3300,11 +3392,11 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -3321,16 +3413,16 @@
         <v>0</v>
       </c>
       <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
         <v>100</v>
-      </c>
-      <c r="X43" s="3">
-        <v>200</v>
       </c>
       <c r="Y43" s="3">
         <v>200</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>4</v>
+      <c r="Z43" s="3">
+        <v>200</v>
       </c>
       <c r="AA43" s="3" t="s">
         <v>4</v>
@@ -3341,8 +3433,11 @@
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3367,8 +3462,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3424,8 +3519,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3435,69 +3533,69 @@
       <c r="E45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G45" s="3">
-        <v>100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J45" s="3">
         <v>200</v>
       </c>
       <c r="K45" s="3">
+        <v>200</v>
+      </c>
+      <c r="L45" s="3">
         <v>5400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1800</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3507,80 +3605,83 @@
       <c r="AC45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>316500</v>
+      </c>
+      <c r="E46" s="3">
         <v>344300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>374000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>270700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>263900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>169200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>197600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>232500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>248100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>274800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>181400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>211300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>247700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>275500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>304400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>330500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>354000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>373600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>125700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>34500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>45400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>54700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>33500</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3590,8 +3691,11 @@
       <c r="AC46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3616,8 +3720,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3673,61 +3777,64 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E48" s="3">
         <v>30200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>37900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>38200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1900</v>
-      </c>
-      <c r="T48" s="3">
-        <v>2000</v>
       </c>
       <c r="U48" s="3">
         <v>2000</v>
@@ -3736,17 +3843,17 @@
         <v>2000</v>
       </c>
       <c r="W48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X48" s="3">
         <v>2100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2100</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3756,8 +3863,11 @@
       <c r="AC48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3839,8 +3949,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,8 +4121,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4014,13 +4133,13 @@
         <v>4300</v>
       </c>
       <c r="E52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1000</v>
       </c>
       <c r="H52" s="3">
         <v>1000</v>
@@ -4035,50 +4154,50 @@
         <v>1000</v>
       </c>
       <c r="L52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M52" s="3">
         <v>1200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>1200</v>
       </c>
       <c r="R52" s="3">
         <v>1200</v>
       </c>
       <c r="S52" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>3400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>100</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4088,8 +4207,11 @@
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,80 +4293,83 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>350100</v>
+      </c>
+      <c r="E54" s="3">
         <v>378800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>406100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>304100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>297700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>203800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>233000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>268800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>285100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>312700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>220700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>250600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>287000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>310200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>331800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>333100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>355900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>375600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>131100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>39500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>49900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>58600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35700</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4254,8 +4379,11 @@
       <c r="AC54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,80 +4445,81 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E57" s="3">
         <v>6700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2200</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4399,35 +4529,38 @@
       <c r="AC57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2400</v>
-      </c>
-      <c r="E58" s="3">
-        <v>2300</v>
       </c>
       <c r="F58" s="3">
         <v>2300</v>
       </c>
       <c r="G58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H58" s="3">
         <v>2200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4482,80 +4615,83 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>200</v>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I59" s="3">
         <v>200</v>
       </c>
       <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3100</v>
-      </c>
-      <c r="W59" s="3">
-        <v>2600</v>
       </c>
       <c r="X59" s="3">
         <v>2600</v>
       </c>
       <c r="Y59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Z59" s="3">
         <v>1700</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4565,80 +4701,83 @@
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E60" s="3">
         <v>20000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3900</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4648,35 +4787,38 @@
       <c r="AC60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E61" s="3">
         <v>27200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>27900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>28500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>29200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>29800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>30400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4731,8 +4873,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4757,54 +4902,54 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>31500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>31900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>32400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>32900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>33400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>26200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1600</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4814,8 +4959,11 @@
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,80 +5217,83 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E66" s="3">
         <v>47200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>47000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>48300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>53900</v>
       </c>
       <c r="K66" s="3">
         <v>53900</v>
       </c>
       <c r="L66" s="3">
+        <v>53900</v>
+      </c>
+      <c r="M66" s="3">
         <v>52100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>50000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>36400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5500</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5146,8 +5303,11 @@
       <c r="AC66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5400,23 +5567,23 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>235100</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>144300</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>144000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>143700</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>112100</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5426,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,80 +5679,83 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-710700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-662100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-627300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-597700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-572500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-544600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-512100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-476900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-438300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-403900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-368800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-331700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-296300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-258900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-223300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-192000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-166000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-142800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-127200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-114900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-102600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-93600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-83500</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5592,8 +5765,11 @@
       <c r="AC72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,80 +6023,83 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>293100</v>
+      </c>
+      <c r="E76" s="3">
         <v>331600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>361100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>262400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>250600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>156800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>184700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>214900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>231200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>260600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>168000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>200600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>231900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>264500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>295300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>321500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>344300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>365500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-117900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-112400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-100500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-91800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-81900</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5924,8 +6109,11 @@
       <c r="AC76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-29600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-32500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-35200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-38700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-34400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-35100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-37100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-35400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-37400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-35600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-31300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-26100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-22000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6406,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6251,19 +6449,19 @@
         <v>500</v>
       </c>
       <c r="P83" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q83" s="3">
         <v>600</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>500</v>
       </c>
       <c r="R83" s="3">
         <v>500</v>
       </c>
       <c r="S83" s="3">
+        <v>500</v>
+      </c>
+      <c r="T83" s="3">
         <v>300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>100</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -6290,10 +6488,13 @@
         <v>100</v>
       </c>
       <c r="AC83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6920,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-21700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-23500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-36400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-33000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-27100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-28200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-28300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-29700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-24700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-23400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-19300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-13600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-10200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,22 +7040,23 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>4</v>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -6845,58 +7065,58 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -6904,8 +7124,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,82 +7296,85 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-45900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-96600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-77300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>47800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>19500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-43600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>14100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>68300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>33700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-83100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-37600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-82900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -7153,8 +7382,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7210,8 +7443,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7267,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,91 +7758,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>123700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>32400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>117600</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>17600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>122700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>259800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>101700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>29200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>44800</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7682,87 +7930,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-77800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-73200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>92000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-30500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-70600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>106000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>38000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-107100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-60700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-102100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>245900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>91400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-10600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-9700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>22200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>39900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>ANNX</t>
   </si>
@@ -656,132 +656,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -809,8 +813,8 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -866,8 +870,11 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -952,8 +959,11 @@
       <c r="AD9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1038,8 +1048,11 @@
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E12" s="3">
         <v>43400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>25000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>21000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>27900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>30300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>28500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>27600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>18000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>11800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>6000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1271,8 +1291,8 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1289,8 +1309,8 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
@@ -1307,29 +1327,32 @@
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-200</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1358,7 +1381,7 @@
         <v>500</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E17" s="3">
         <v>52500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>39400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>33600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>28600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>41200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>37400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>35400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>31400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-52500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-39400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-33600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-28600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-34800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-37700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-41200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-36700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-36100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-37400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-35400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-35700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-31400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-26200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-23200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-15600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-12200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-12500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,8 +1680,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1676,17 +1710,17 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>2300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
@@ -1701,126 +1735,132 @@
         <v>100</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-56900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-51900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-38900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-33000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-28000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-29500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-34200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-37200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-40700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-33900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-34500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-36600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-34900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-36900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-35000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-30800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-25500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-22900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-15500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-12100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-12200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1848,8 +1888,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1905,94 +1945,100 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-48600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-29600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-25200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-27900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-35200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-38700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-34400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-35100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-37100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-35400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-37400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-35600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-31300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-26100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-23200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-15600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-12200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-12300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2020,14 +2066,14 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>4</v>
@@ -2035,8 +2081,8 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2077,8 +2123,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-48600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-29600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-27900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-32500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-35200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-38700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-35100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-37100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-35400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-37400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-35600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-31300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-26100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-23200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-15600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-12300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-48600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-29600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-27900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-32500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-35200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-38700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-35100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-37100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-35400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-37400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-35600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-31300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-26100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-23200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-22000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,8 +2746,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2708,17 +2778,17 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-2300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
@@ -2733,126 +2803,132 @@
         <v>-100</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-48600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-29600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-27900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-32500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-35200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-38700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-35100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-37100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-35400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-37400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-35600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-31300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-26100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-23200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-22000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-12600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-48600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-29600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-27900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-32500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-35200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-38700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-35100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-37100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-35400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-37400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-35600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-31300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-26100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-23200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-22000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-12600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,83 +3264,84 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>97100</v>
+      </c>
+      <c r="E41" s="3">
         <v>49500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>79500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>157300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>151900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>225100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>133200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>113600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>144100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>140000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>210700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>104600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>112800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>74800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>68500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>99600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>206700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>268600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>370700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>124800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>33300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>53700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>31500</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3264,65 +3351,68 @@
       <c r="AD41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>166600</v>
+      </c>
+      <c r="E42" s="3">
         <v>262500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>260600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>211400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>113000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>34600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>32100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>79300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>84000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>102600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>58900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>73000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>93800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>167900</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>202800</v>
       </c>
       <c r="R42" s="3">
         <v>202800</v>
       </c>
       <c r="S42" s="3">
+        <v>202800</v>
+      </c>
+      <c r="T42" s="3">
         <v>120000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>82600</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3335,8 +3425,8 @@
       <c r="Y42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3350,8 +3440,11 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3379,8 +3472,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3395,11 +3488,11 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
@@ -3416,16 +3509,16 @@
         <v>0</v>
       </c>
       <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
         <v>100</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>200</v>
       </c>
       <c r="Z43" s="3">
         <v>200</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>4</v>
+      <c r="AA43" s="3">
+        <v>200</v>
       </c>
       <c r="AB43" s="3" t="s">
         <v>4</v>
@@ -3436,8 +3529,11 @@
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3465,8 +3561,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3522,8 +3618,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3536,69 +3635,69 @@
       <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
       </c>
       <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
         <v>5400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1800</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3608,83 +3707,86 @@
       <c r="AD45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>268200</v>
+      </c>
+      <c r="E46" s="3">
         <v>316500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>344300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>374000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>270700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>263900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>169200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>197600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>232500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>248100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>274800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>181400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>211300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>247700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>275500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>304400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>330500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>354000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>373600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>125700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>34500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>45400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>54700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>33500</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3694,8 +3796,11 @@
       <c r="AD46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3723,8 +3828,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3780,64 +3885,67 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E48" s="3">
         <v>29300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>37300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>38200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>32900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1900</v>
-      </c>
-      <c r="U48" s="3">
-        <v>2000</v>
       </c>
       <c r="V48" s="3">
         <v>2000</v>
@@ -3846,17 +3954,17 @@
         <v>2000</v>
       </c>
       <c r="X48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y48" s="3">
         <v>2100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2100</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3866,8 +3974,11 @@
       <c r="AD48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,25 +4241,28 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4300</v>
+        <v>6300</v>
       </c>
       <c r="E52" s="3">
         <v>4300</v>
       </c>
       <c r="F52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1000</v>
       </c>
       <c r="I52" s="3">
         <v>1000</v>
@@ -4157,50 +4277,50 @@
         <v>1000</v>
       </c>
       <c r="M52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N52" s="3">
         <v>1200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1800</v>
-      </c>
-      <c r="R52" s="3">
-        <v>1200</v>
       </c>
       <c r="S52" s="3">
         <v>1200</v>
       </c>
       <c r="T52" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>3400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>100</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,83 +4419,86 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>303000</v>
+      </c>
+      <c r="E54" s="3">
         <v>350100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>378800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>406100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>304100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>297700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>203800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>233000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>268800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>285100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>312700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>220700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>250600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>287000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>310200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>331800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>333100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>355900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>375600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>131100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>39500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>49900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>58600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>35700</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,8 +4576,9 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4455,74 +4586,74 @@
         <v>10400</v>
       </c>
       <c r="E57" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F57" s="3">
         <v>6700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2200</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4532,38 +4663,41 @@
       <c r="AD57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E58" s="3">
         <v>2500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2400</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2300</v>
       </c>
       <c r="G58" s="3">
         <v>2300</v>
       </c>
       <c r="H58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I58" s="3">
         <v>2200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4618,8 +4752,11 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4629,72 +4766,72 @@
       <c r="E59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3">
-        <v>200</v>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J59" s="3">
         <v>200</v>
       </c>
       <c r="K59" s="3">
+        <v>200</v>
+      </c>
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3100</v>
-      </c>
-      <c r="X59" s="3">
-        <v>2600</v>
       </c>
       <c r="Y59" s="3">
         <v>2600</v>
       </c>
       <c r="Z59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1700</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4704,83 +4841,86 @@
       <c r="AD59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E60" s="3">
         <v>30500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3900</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4790,38 +4930,41 @@
       <c r="AD60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E61" s="3">
         <v>26500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>27200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>27900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>29200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>29800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4876,8 +5019,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4905,54 +5051,54 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>31500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>31900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>32400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>32900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>33800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>26200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1600</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,83 +5375,86 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E66" s="3">
         <v>57000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>41700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>47100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>48300</v>
-      </c>
-      <c r="K66" s="3">
-        <v>53900</v>
       </c>
       <c r="L66" s="3">
         <v>53900</v>
       </c>
       <c r="M66" s="3">
+        <v>53900</v>
+      </c>
+      <c r="N66" s="3">
         <v>52100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>50000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>36400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5500</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5570,23 +5738,23 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>235100</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>144300</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>144000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>143700</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>112100</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,83 +5853,86 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-765100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-710700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-662100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-627300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-597700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-572500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-544600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-512100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-476900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-438300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-403900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-368800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-331700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-296300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-258900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-223300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-192000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-166000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-142800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-127200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-114900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-102600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-93600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-83500</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,83 +6209,86 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>243800</v>
+      </c>
+      <c r="E76" s="3">
         <v>293100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>331600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>361100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>262400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>250600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>156800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>184700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>214900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>231200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>260600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>168000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>200600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>231900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>264500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>295300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>321500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>344300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>365500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-117900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-112400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-100500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-91800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-81900</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-48600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-29600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-27900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-32500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-35200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-38700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-35100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-37100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-35400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-37400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-35600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-31300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-26100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-23200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-22000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-12600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6452,19 +6651,19 @@
         <v>500</v>
       </c>
       <c r="Q83" s="3">
+        <v>500</v>
+      </c>
+      <c r="R83" s="3">
         <v>600</v>
-      </c>
-      <c r="R83" s="3">
-        <v>500</v>
       </c>
       <c r="S83" s="3">
         <v>500</v>
       </c>
       <c r="T83" s="3">
+        <v>500</v>
+      </c>
+      <c r="U83" s="3">
         <v>300</v>
-      </c>
-      <c r="U83" s="3">
-        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -6491,10 +6690,13 @@
         <v>100</v>
       </c>
       <c r="AD83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-50100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-36000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-32000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-21700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-28300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-23500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-36400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-33000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-27100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-30700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-29700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-24700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-23400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-19300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-13600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-10000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,25 +7261,26 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -7068,58 +7289,58 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,85 +7526,88 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>97600</v>
+      </c>
+      <c r="E94" s="3">
         <v>1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-45900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-96600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-77300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>47800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>5500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>19500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-43600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>14100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>68300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>33700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-83100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-37600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-82900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -7385,8 +7615,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7446,8 +7680,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,94 +8004,100 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>5000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>123700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>32400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>117600</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>17600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>122700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>259800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>101700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>29200</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>44800</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7933,90 +8182,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-30000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-77800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-73200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>92000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-30500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-70600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>106000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>38000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-31100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-107100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-60700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-102100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>245900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>91400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-10600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>22200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>39900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
   <si>
     <t>ANNX</t>
   </si>
@@ -656,136 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -816,8 +820,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -873,8 +877,11 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -962,8 +969,11 @@
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E12" s="3">
         <v>48200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>43400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>25000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>21000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>27900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>30300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>32300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>29100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>27200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>27600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>24600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>18000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>11800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1294,8 +1314,8 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1312,8 +1332,8 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
@@ -1330,29 +1350,32 @@
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-200</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>4</v>
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1384,7 +1407,7 @@
         <v>500</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E17" s="3">
         <v>57400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>52500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>39400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>41200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>37500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>35700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>31400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>26200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-51700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-57400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-52500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-39400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-33600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-28600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-30000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-34800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-37700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-41200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-36700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-36100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-37400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-37500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-35700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-31400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-26200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-23200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-15600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-12200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1713,17 +1747,17 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>2300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
@@ -1738,129 +1772,135 @@
         <v>100</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-51200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-56900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-51900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-38900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-33000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-28000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-29500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-34200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-37200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-40700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-33900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-34500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-36600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-34900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-36900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-35000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-30800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-25500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-22900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-15500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-12100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-8500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1891,8 +1931,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1948,97 +1988,103 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-54400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-48600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-34800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-29600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-25200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-27900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-35200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-38700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-34400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-35100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-37100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-37400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-35600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-31300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-26100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-23200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-15600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-12200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-9400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2069,14 +2115,14 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>4</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>4</v>
@@ -2084,8 +2130,8 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-54400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-48600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-29600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-27900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-32500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-35200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-38700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-34400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-35100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-37100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-37400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-35600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-31300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-26100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-23200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-15600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-12200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-54400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-48600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-29600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-27900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-32500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-35200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-38700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-35100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-37100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-37400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-35600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-31300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-26100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-23200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-22000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2781,17 +2851,17 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-2300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
@@ -2806,129 +2876,135 @@
         <v>-100</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>1100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-54400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-48600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-29600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-27900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-32500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-35200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-38700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-35100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-37100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-37400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-35600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-31300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-26100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-23200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-22000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-12500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-54400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-48600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-29600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-27900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-32500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-35200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-38700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-35100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-37100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-37400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-35600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-31300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-26100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-23200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-22000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-12500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,86 +3351,87 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>132300</v>
+      </c>
+      <c r="E41" s="3">
         <v>97100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>79500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>157300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>151900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>225100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>133200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>113600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>144100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>140000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>210700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>104600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>112800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>74800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>68500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>99600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>206700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>268600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>370700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>124800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>33300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>43900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>53700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>31500</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3354,68 +3441,71 @@
       <c r="AE41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E42" s="3">
         <v>166600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>262500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>260600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>211400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>113000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>34600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>32100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>79300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>84000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>102600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>58900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>73000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>93800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>167900</v>
-      </c>
-      <c r="R42" s="3">
-        <v>202800</v>
       </c>
       <c r="S42" s="3">
         <v>202800</v>
       </c>
       <c r="T42" s="3">
+        <v>202800</v>
+      </c>
+      <c r="U42" s="3">
         <v>120000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>82600</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3428,8 +3518,8 @@
       <c r="Z42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3475,8 +3568,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3491,11 +3584,11 @@
         <v>0</v>
       </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
@@ -3512,16 +3605,16 @@
         <v>0</v>
       </c>
       <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
         <v>100</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>200</v>
       </c>
       <c r="AA43" s="3">
         <v>200</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>4</v>
+      <c r="AB43" s="3">
+        <v>200</v>
       </c>
       <c r="AC43" s="3" t="s">
         <v>4</v>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3564,8 +3660,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3638,69 +3737,69 @@
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
       </c>
       <c r="M45" s="3">
+        <v>200</v>
+      </c>
+      <c r="N45" s="3">
         <v>5400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1800</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3710,86 +3809,89 @@
       <c r="AE45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>230600</v>
+      </c>
+      <c r="E46" s="3">
         <v>268200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>316500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>344300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>374000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>270700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>263900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>169200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>197600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>232500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>248100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>274800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>181400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>211300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>247700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>275500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>304400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>330500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>354000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>373600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>125700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>34500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>45400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>54700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>33500</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3799,8 +3901,11 @@
       <c r="AE46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3831,8 +3936,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3888,67 +3993,70 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E48" s="3">
         <v>28500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>36700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>37900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>38200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>32900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1900</v>
-      </c>
-      <c r="V48" s="3">
-        <v>2000</v>
       </c>
       <c r="W48" s="3">
         <v>2000</v>
@@ -3957,17 +4065,17 @@
         <v>2000</v>
       </c>
       <c r="Y48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z48" s="3">
         <v>2100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2100</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4253,19 +4373,19 @@
         <v>6300</v>
       </c>
       <c r="E52" s="3">
-        <v>4300</v>
+        <v>6300</v>
       </c>
       <c r="F52" s="3">
         <v>4300</v>
       </c>
       <c r="G52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H52" s="3">
         <v>1000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1000</v>
       </c>
       <c r="J52" s="3">
         <v>1000</v>
@@ -4280,50 +4400,50 @@
         <v>1000</v>
       </c>
       <c r="N52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O52" s="3">
         <v>1200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1800</v>
-      </c>
-      <c r="S52" s="3">
-        <v>1200</v>
       </c>
       <c r="T52" s="3">
         <v>1200</v>
       </c>
       <c r="U52" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
       </c>
       <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
         <v>3400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>100</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,86 +4545,89 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>264600</v>
+      </c>
+      <c r="E54" s="3">
         <v>303000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>350100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>378800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>406100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>304100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>297700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>203800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>233000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>268800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>285100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>312700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>220700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>250600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>287000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>310200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>331800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>333100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>355900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>375600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>131100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>39500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>49900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>58600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>35700</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,86 +4707,87 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10400</v>
+        <v>11500</v>
       </c>
       <c r="E57" s="3">
         <v>10400</v>
       </c>
       <c r="F57" s="3">
+        <v>10400</v>
+      </c>
+      <c r="G57" s="3">
         <v>6700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2200</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4666,41 +4797,44 @@
       <c r="AE57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2300</v>
       </c>
       <c r="H58" s="3">
         <v>2300</v>
       </c>
       <c r="I58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J58" s="3">
         <v>2200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1500</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4755,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4769,72 +4906,72 @@
       <c r="F59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3">
-        <v>200</v>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>200</v>
       </c>
       <c r="L59" s="3">
+        <v>200</v>
+      </c>
+      <c r="M59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3100</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>2600</v>
       </c>
       <c r="Z59" s="3">
         <v>2600</v>
       </c>
       <c r="AA59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AB59" s="3">
         <v>1700</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4844,86 +4981,89 @@
       <c r="AE59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E60" s="3">
         <v>33500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3900</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4933,41 +5073,44 @@
       <c r="AE60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E61" s="3">
         <v>25700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>26500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>27200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>27900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>28500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>29200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>29800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5054,54 +5200,54 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>31500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>31900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>32400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>32900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>33400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>33800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>26200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1600</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,86 +5533,89 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E66" s="3">
         <v>59200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>41700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>48300</v>
-      </c>
-      <c r="L66" s="3">
-        <v>53900</v>
       </c>
       <c r="M66" s="3">
         <v>53900</v>
       </c>
       <c r="N66" s="3">
+        <v>53900</v>
+      </c>
+      <c r="O66" s="3">
         <v>52100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>50000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>55100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>45700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>36400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5500</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5741,23 +5909,23 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>235100</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>144300</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>144000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>143700</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>112100</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,86 +6027,89 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-814200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-765100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-710700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-662100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-627300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-597700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-572500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-544600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-512100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-476900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-438300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-403900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-368800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-331700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-296300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-258900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-223300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-192000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-166000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-142800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-127200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-114900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-102600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-93600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-83500</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,86 +6395,89 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>199000</v>
+      </c>
+      <c r="E76" s="3">
         <v>243800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>293100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>331600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>361100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>262400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>250600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>156800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>184700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>214900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>231200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>260600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>168000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>200600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>231900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>264500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>295300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>321500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>344300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>365500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-117900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-112400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-100500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-91800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-81900</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-54400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-48600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-29600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-27900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-32500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-35200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-38700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-35100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-37100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-37400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-35600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-31300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-26100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-23200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-22000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-12500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6654,19 +6853,19 @@
         <v>500</v>
       </c>
       <c r="R83" s="3">
+        <v>500</v>
+      </c>
+      <c r="S83" s="3">
         <v>600</v>
-      </c>
-      <c r="S83" s="3">
-        <v>500</v>
       </c>
       <c r="T83" s="3">
         <v>500</v>
       </c>
       <c r="U83" s="3">
+        <v>500</v>
+      </c>
+      <c r="V83" s="3">
         <v>300</v>
-      </c>
-      <c r="V83" s="3">
-        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
@@ -6693,10 +6892,13 @@
         <v>100</v>
       </c>
       <c r="AE83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-50100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-36000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-32000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-21700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-23500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-36400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-33000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-27100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-28200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-30300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-28300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-29700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-24700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-23400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-19300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-13600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-10200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,28 +7482,29 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>4</v>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -7292,58 +7513,58 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,88 +7756,91 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E94" s="3">
         <v>97600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-45900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-96600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-77300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>47800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>19500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-43600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>14100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>19700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>68300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>33700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-83100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-37600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-82900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7683,8 +7917,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,97 +8250,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>123700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>32400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>117600</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>17600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>122700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>259800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>101700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>29200</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>44800</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E102" s="3">
         <v>47600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-30000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-77800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-73200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>92000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-70600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>106000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>38000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-31100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-107100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-60700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-102100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>245900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>91400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-10600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>22200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>39900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANNX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>ANNX</t>
   </si>
@@ -656,144 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -830,11 +837,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -887,8 +894,14 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -982,8 +995,14 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1096,14 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,103 +1137,111 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>42700</v>
+      </c>
+      <c r="F12" s="3">
         <v>49700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>44200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>48200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>43400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>30100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>25000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>21000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>23300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>27900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>30300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>32300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>28500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>27900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>29100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>27000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>27200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>27600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>24600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>20700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>18000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>11800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>9300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>10200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>6800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>7100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>6000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>4700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>3900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>3800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1335,14 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1340,11 +1379,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1358,11 +1397,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
@@ -1376,29 +1415,35 @@
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-200</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1436,10 +1481,10 @@
         <v>500</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1492,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1575,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>50300</v>
+      </c>
+      <c r="F17" s="3">
         <v>57000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>51700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>57400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>52500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>39400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>33600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>28600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>30000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>34800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>37700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>41200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>36700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>36100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>37400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>35400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>37500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>35700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>31400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>26200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>23200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>15600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>12200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>12500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>8900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>9100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>8200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>6100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>4900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>4600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-46100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-50300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-57000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-51700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-57400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-52500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-39400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-33600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-28600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-30000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-34800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-37700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-41200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-36700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-37400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-35400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-37500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-35700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-31400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-26200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-23200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-15600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-9100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1814,10 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1787,20 +1854,20 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>2300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
@@ -1812,135 +1879,147 @@
         <v>100</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-56500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-51200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-56900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-51900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-38900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-33000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-28000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-29500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-34200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-37200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-40700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-33900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-36600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-34900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-36900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-35000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-30800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-25500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-22900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-12100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1977,11 +2056,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2034,103 +2113,115 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-54900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-49200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-54400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-48600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-34800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-29600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-25200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-27900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-32500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-35200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-38700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-34400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-35100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-37100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-35400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-37400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-35600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-31300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-26100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-23200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-15600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-9400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2167,26 +2258,26 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>4</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -2224,8 +2315,14 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2416,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-54900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-49200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-54400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-48600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-34800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-29600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-25200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-27900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-32500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-35200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-38700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-34400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-35100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-37100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-35400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-37400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-35600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-31300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-26100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-23200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-15600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-54900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-51000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-54400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-48600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-34800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-29600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-25200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-27900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-32500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-35200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-38700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-34400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-35100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-37100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-35400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-37400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-35600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-31300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-26100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-23200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +3022,14 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2927,20 +3066,20 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-2300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
@@ -2952,135 +3091,147 @@
         <v>-100</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>1100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>2500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-54900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-49200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-54400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-48600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-34800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-29600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-25200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-27900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-32500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-35200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-38700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-34400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-35100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-37100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-35400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-37400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-35600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-31300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-26100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-23200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3325,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-54900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-49200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-54400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-48600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-34800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-29600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-25200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-27900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-32500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-35200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-38700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-34400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-35100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-37100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-35400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-37400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-35600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-31300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-26100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-23200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,172 +3610,180 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>175200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>162100</v>
+      </c>
+      <c r="F41" s="3">
         <v>139400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>132300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>97100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>49500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>79500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>157300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>151900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>225100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>133200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>113600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>144100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>140000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>210700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>104600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>112800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>74800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>68500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>99600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>206700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>268600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>370700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>124800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>33300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>43900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>53700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>31500</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>76300</v>
+      </c>
+      <c r="F42" s="3">
         <v>49300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>94700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>166600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>262500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>260600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>211400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>113000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>34600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>32100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>79300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>84000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>102600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>58900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>73000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>93800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>167900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>202800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>202800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>120000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>82600</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3614,11 +3793,11 @@
       <c r="AB42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -3629,8 +3808,14 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3667,11 +3852,11 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -3683,14 +3868,14 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
@@ -3704,28 +3889,34 @@
         <v>0</v>
       </c>
       <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
         <v>100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>200</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3762,11 +3953,11 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3819,8 +4010,14 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3842,8 +4039,8 @@
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
@@ -3851,166 +4048,178 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>5400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>5300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>3800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>4600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>5000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>3800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>2900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1800</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>228300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>242200</v>
+      </c>
+      <c r="F46" s="3">
         <v>192800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>230600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>268200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>316500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>344300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>374000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>270700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>263900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>169200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>197600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>232500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>248100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>274800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>181400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>211300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>247700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>275500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>304400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>330500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>354000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>373600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>125700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>34500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>45400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>54700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>33500</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4047,11 +4256,11 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4104,94 +4313,100 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>25800</v>
+      </c>
+      <c r="F48" s="3">
         <v>26700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>27600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>28500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>29300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>30200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>31100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>31900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>32800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>33600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>34400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>35200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>36000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>36700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>37300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>37900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>38200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>32900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>26200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1900</v>
-      </c>
-      <c r="X48" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>2000</v>
       </c>
       <c r="Z48" s="3">
         <v>2000</v>
       </c>
       <c r="AA48" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AB48" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="AC48" s="3">
         <v>2100</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
+      <c r="AD48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AE48" s="3">
+        <v>2100</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>4</v>
@@ -4199,8 +4414,14 @@
       <c r="AG48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4515,14 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,37 +4717,43 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E52" s="3">
         <v>9600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G52" s="3">
         <v>6300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>6300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>4300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>4300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1400</v>
       </c>
       <c r="K52" s="3">
         <v>1000</v>
       </c>
       <c r="L52" s="3">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="M52" s="3">
         <v>1000</v>
@@ -4526,61 +4765,67 @@
         <v>1000</v>
       </c>
       <c r="P52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R52" s="3">
         <v>1200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1400</v>
-      </c>
-      <c r="S52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1800</v>
       </c>
       <c r="U52" s="3">
         <v>1200</v>
       </c>
       <c r="V52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="W52" s="3">
         <v>1200</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
       <c r="X52" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
         <v>3400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>100</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4919,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>262900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>277600</v>
+      </c>
+      <c r="F54" s="3">
         <v>229100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>264600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>303000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>350100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>378800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>406100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>304100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>297700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>203800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>233000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>268800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>285100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>312700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>220700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>250600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>287000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>310200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>331800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>333100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>355900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>375600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>131100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>39500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>49900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>58600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>35700</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,145 +5098,153 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F57" s="3">
         <v>18200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>11500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>10400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>10400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>7200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>10300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>7400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>6900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>10300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>9400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>11200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>4200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>4500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>3700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>4000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>3300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>2400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>2600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>2200</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1500</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5029,8 +5296,14 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5049,220 +5322,232 @@
       <c r="H59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>14900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>13300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>10000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>7700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>10600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>7100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>6100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>6200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>6900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>5000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>9600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>3100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1700</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>42600</v>
+      </c>
+      <c r="F60" s="3">
         <v>43600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>40600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>33500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>30500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>20000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>17100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>13100</v>
-      </c>
-      <c r="K60" s="3">
-        <v>17900</v>
-      </c>
-      <c r="L60" s="3">
-        <v>17200</v>
       </c>
       <c r="M60" s="3">
         <v>17900</v>
       </c>
       <c r="N60" s="3">
+        <v>17200</v>
+      </c>
+      <c r="O60" s="3">
+        <v>17900</v>
+      </c>
+      <c r="P60" s="3">
         <v>22900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>22400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>20200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>20300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>17100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>21700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>11900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>10300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>10700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>10600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>9000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>12700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>6300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>4900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>5100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>3900</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F61" s="3">
         <v>24100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>24900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>25700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>26500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>27200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>27900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>28500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>29200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>29800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>30400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>31000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5314,8 +5599,14 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5352,65 +5643,71 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3">
         <v>31500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>31900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>32400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>32900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>33400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>33800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>26200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1600</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>65900</v>
+      </c>
+      <c r="F66" s="3">
         <v>67700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>65600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>59200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>57000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>47200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>45000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>41700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>47100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>47000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>48300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>53900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>53900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>52100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>52700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>50000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>55100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>45700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>36400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>11600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>11700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>10100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>13900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>7700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>6400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>6700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>5500</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6083,34 +6418,40 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>235100</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AB70" s="3">
         <v>144300</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AC70" s="3">
         <v>144000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AD70" s="3">
         <v>143700</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AE70" s="3">
         <v>112100</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
       <c r="AF70" s="3">
         <v>0</v>
       </c>
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6545,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-961500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-917400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-869100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-814200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-765100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-710700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-662100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-627300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-597700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-572500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-544600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-512100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-476900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-438300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-403900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-368800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-331700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-296300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-258900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-223300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-192000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-166000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-142800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-127200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-114900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-102600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-93600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-83500</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>204500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>211600</v>
+      </c>
+      <c r="F76" s="3">
         <v>161400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>199000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>243800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>293100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>331600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>361100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>262400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>250600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>156800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>184700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>214900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>231200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>260600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>168000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>200600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>231900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>264500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>295300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>321500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>344300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>365500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-117900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-112400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-100500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-91800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-81900</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +7151,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-54900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-49200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-54400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-48600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-34800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-29600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-25200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-27900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-32500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-35200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-38700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-34400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-35100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-37100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-35400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-37400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-35600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-31300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-26100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-23200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7399,10 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7058,22 +7455,22 @@
         <v>500</v>
       </c>
       <c r="T83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="U83" s="3">
         <v>500</v>
       </c>
       <c r="V83" s="3">
+        <v>600</v>
+      </c>
+      <c r="W83" s="3">
         <v>500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y83" s="3">
         <v>300</v>
-      </c>
-      <c r="X83" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
@@ -7097,10 +7494,16 @@
         <v>100</v>
       </c>
       <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +8001,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-45900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-52300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-38100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-50100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-36000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-32000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-21700</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-28300</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-23500</v>
       </c>
       <c r="L89" s="3">
         <v>-28300</v>
       </c>
       <c r="M89" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="O89" s="3">
         <v>-36400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-33000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-27100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-28200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-30300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-28300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-29700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-24700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-23400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-19300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-13600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +8143,111 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-900</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-5200</v>
       </c>
       <c r="S91" s="3">
         <v>-900</v>
       </c>
       <c r="T91" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="U91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8442,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="F94" s="3">
         <v>45900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>73100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>97600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-45900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-96600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-77300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>47800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>5500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>19500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-43600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>14100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>19700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>68300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>33700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-83100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-37600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-82900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>0</v>
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8157,11 +8624,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8214,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,108 +8984,120 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>95100</v>
+      </c>
+      <c r="F100" s="3">
         <v>13600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>5000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>123700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>32400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>117600</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>17600</v>
-      </c>
-      <c r="O100" s="3">
-        <v>100</v>
-      </c>
-      <c r="P100" s="3">
-        <v>122700</v>
       </c>
       <c r="Q100" s="3">
         <v>100</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>122700</v>
       </c>
       <c r="S100" s="3">
+        <v>100</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>300</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>259800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>101700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>29200</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>44800</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -8689,99 +9186,111 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>22600</v>
+      </c>
+      <c r="F102" s="3">
         <v>7100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>35200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>47600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-30000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-77800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>5400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-73200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>92000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>19500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-30500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>4100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-70600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>106000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-8300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>38000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>6300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-31100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-107100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-60700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-102100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>245900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>91400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>22200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>39900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>4600</v>
       </c>
     </row>
